--- a/horse_data.xlsx
+++ b/horse_data.xlsx
@@ -19,12 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy/m/d"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -749,7 +748,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="テーブル4" displayName="テーブル4" ref="A1:G192" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="テーブル4" displayName="テーブル4" ref="A1:G193" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:G184"/>
   <tableColumns count="7">
     <tableColumn id="1" name="馬名"/>
@@ -781,7 +780,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="テーブル79" displayName="テーブル79" ref="A1:D189" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="テーブル79" displayName="テーブル79" ref="A1:D190" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:D182"/>
   <sortState ref="A2:D34">
     <sortCondition ref="A1:A34"/>
@@ -3598,7 +3597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="24.109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4175,25 +4174,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>アローメタル</t>
+          <t>アルバンヌ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>45044</v>
+        <v>44992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>アドマイヤマーズ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ミスベジル</t>
+          <t>プティフォリー</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4203,67 +4202,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>木村 哲也</t>
+          <t>田中 博康</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>アンシール</t>
+          <t>アローメタル</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>44308</v>
+        <v>45044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>パイロ</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>トラディション</t>
+          <t>ミスベジル</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>小崎 憲</t>
+          <t>木村 哲也</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>アンリーロード</t>
+          <t>アンシール</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>43906</v>
+        <v>44308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>リアルスティール</t>
+          <t>パイロ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>カシシ</t>
+          <t>トラディション</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4273,32 +4272,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>茶木 太樹</t>
+          <t>小崎 憲</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>アーレムアレス</t>
+          <t>アンリーロード</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>44976</v>
+        <v>43906</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ハービンジャー</t>
+          <t>リアルスティール</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>スターズインヘヴン</t>
+          <t>カシシ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4308,14 +4307,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>橋口 慎介</t>
+          <t>茶木 太樹</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>イベントホライゾン</t>
+          <t>アーレムアレス</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4324,7 +4323,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>45032</v>
+        <v>44976</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4333,7 +4332,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ライツェント</t>
+          <t>スターズインヘヴン</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4343,14 +4342,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>池江 泰寿</t>
+          <t>橋口 慎介</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>イモータリス</t>
+          <t>イベントホライゾン</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4359,86 +4358,86 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>44989</v>
+        <v>45032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ミッキーロケット</t>
+          <t>ハービンジャー</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>シャルルヴォア</t>
+          <t>ライツェント</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>手塚 貴久</t>
+          <t>池江 泰寿</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>インヴォーグ</t>
+          <t>イモータリス</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>44631</v>
+        <v>44989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>ミッキーロケット</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>トレンドハンター</t>
+          <t>シャルルヴォア</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>福永 祐一</t>
+          <t>手塚 貴久</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>イージーライダー</t>
+          <t>インヴォーグ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>44991</v>
+        <v>44631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>エセンテペ</t>
+          <t>トレンドハンター</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4448,14 +4447,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>福永 祐一</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ウォーターデライト</t>
+          <t>イージーライダー</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4464,16 +4463,16 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>45025</v>
+        <v>44991</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ウォーターラボ</t>
+          <t>エセンテペ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4483,14 +4482,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高柳 大輔</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ウォーターリヒト</t>
+          <t>ウォーターデライト</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4499,16 +4498,16 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>44279</v>
+        <v>45025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ドレフォン</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ウォーターピオニー</t>
+          <t>ウォーターラボ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4518,32 +4517,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>石橋 守</t>
+          <t>高柳 大輔</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>エイシンウィスパー</t>
+          <t>ウォーターリヒト</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>45039</v>
+        <v>44279</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ルーラーシップ</t>
+          <t>ドレフォン</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>エイシンカラット</t>
+          <t>ウォーターピオニー</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4553,32 +4552,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>今野 貞一</t>
+          <t>石橋 守</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>エムズビギン</t>
+          <t>エイシンウィスパー</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>45011</v>
+        <v>45039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ルーラーシップ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>デルフィニア2</t>
+          <t>エイシンカラット</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4588,32 +4587,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>友道 康夫</t>
+          <t>今野 貞一</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>エラトー</t>
+          <t>エムズビギン</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>44221</v>
+        <v>45011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Saxon Warrior</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>エライヤ</t>
+          <t>デルフィニア2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4623,32 +4622,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>上村 洋行</t>
+          <t>友道 康夫</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>エルトンバローズ</t>
+          <t>エラトー</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>43908</v>
+        <v>44221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ディープブリランテ</t>
+          <t>Saxon Warrior</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ショウナンカラット</t>
+          <t>エライヤ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4658,32 +4657,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>上村 洋行</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>エンネ</t>
+          <t>エルトンバローズ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>45027</v>
+        <v>43908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>ディープブリランテ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ルパン2</t>
+          <t>ショウナンカラット</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4693,49 +4692,49 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>吉岡 辰弥</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>エーデルゼーレ</t>
+          <t>エンネ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>44981</v>
+        <v>45027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>コントレイル</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>カラライナ</t>
+          <t>ルパン2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>堀 宣行</t>
+          <t>吉岡 辰弥</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>オウギノカナメ</t>
+          <t>エーデルゼーレ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4744,16 +4743,16 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>43922</v>
+        <v>44981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>コントレイル</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ジェラスガール</t>
+          <t>カラライナ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4763,14 +4762,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高木 登</t>
+          <t>堀 宣行</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>オフトレイル</t>
+          <t>オウギノカナメ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4779,103 +4778,103 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>44330</v>
+        <v>43922</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Farhh</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rose Trail</t>
+          <t>ジェラスガール</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>吉村 圭司</t>
+          <t>高木 登</t>
         </is>
       </c>
     </row>
     <row r="35" ht="13.5" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>オブラプリーマ</t>
+          <t>オフトレイル</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>45028</v>
+        <v>44330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ヴァンゴッホ</t>
+          <t>Farhh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>マナローラ</t>
+          <t>Rose Trail</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>上原 佑紀</t>
+          <t>吉村 圭司</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>オメガインペリアル</t>
+          <t>オブラプリーマ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>44284</v>
+        <v>45028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kingman</t>
+          <t>ヴァンゴッホ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nuovo Record</t>
+          <t>マナローラ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>安田 翔伍</t>
+          <t>上原 佑紀</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>オリオンブレード</t>
+          <t>オメガインペリアル</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4884,16 +4883,16 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>45020</v>
+        <v>44284</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>Kingman</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>アンブラッセモワ</t>
+          <t>Nuovo Record</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4903,14 +4902,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>矢作 芳人</t>
+          <t>安田 翔伍</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>オルフセン</t>
+          <t>オリオンブレード</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4919,51 +4918,51 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>45019</v>
+        <v>45020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>スターズアラインド</t>
+          <t>アンブラッセモワ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>斎藤 誠</t>
+          <t>矢作 芳人</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>オーケーバーディー</t>
+          <t>オルフセン</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>44278</v>
+        <v>45019</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>シニスターミニスター</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>セラファン</t>
+          <t>スターズアラインド</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4973,14 +4972,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>斎藤 誠</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>オーケーマヒナ</t>
+          <t>オーケーバーディー</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4989,16 +4988,16 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>44667</v>
+        <v>44278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>モズアスコット</t>
+          <t>シニスターミニスター</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ヒアーズトウショウ</t>
+          <t>セラファン</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5015,7 +5014,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>カシノリアーナ</t>
+          <t>オーケーマヒナ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5024,16 +5023,16 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>44988</v>
+        <v>44667</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>サトノクラウン</t>
+          <t>モズアスコット</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ミュゼミランダ</t>
+          <t>ヒアーズトウショウ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5043,84 +5042,84 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>天間 昭一</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>カットソロ</t>
+          <t>カシノリアーナ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>45017</v>
+        <v>44988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>コントレイル</t>
+          <t>サトノクラウン</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>スルターナ</t>
+          <t>ミュゼミランダ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>矢作 芳人</t>
+          <t>天間 昭一</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>カニキュル</t>
+          <t>カットソロ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>44321</v>
+        <v>45017</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>コントレイル</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>シャルール</t>
+          <t>スルターナ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>菊沢 隆徳</t>
+          <t>矢作 芳人</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>カネラフィーナ</t>
+          <t>カニキュル</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5129,16 +5128,16 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>44604</v>
+        <v>44321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Frankel</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ジョイカネラ</t>
+          <t>シャルール</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5148,49 +5147,49 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>手塚 貴久</t>
+          <t>菊沢 隆徳</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>カレントゥルーシー</t>
+          <t>カネラフィーナ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>44995</v>
+        <v>44604</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>サングレーザー</t>
+          <t>Frankel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>カレンシリエージョ</t>
+          <t>ジョイカネラ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>鈴木 孝志</t>
+          <t>手塚 貴久</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>カヴァレリッツォ</t>
+          <t>カレントゥルーシー</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5199,16 +5198,16 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>44985</v>
+        <v>44995</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>サートゥルナーリア</t>
+          <t>サングレーザー</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>バラーディスト</t>
+          <t>カレンシリエージョ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5218,14 +5217,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>吉岡 辰弥</t>
+          <t>鈴木 孝志</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ガウディ</t>
+          <t>カヴァレリッツォ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5234,16 +5233,16 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>45007</v>
+        <v>44985</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>レイデオロ</t>
+          <t>サートゥルナーリア</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>グラディーヴァ</t>
+          <t>バラーディスト</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5253,14 +5252,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>上村 洋行</t>
+          <t>吉岡 辰弥</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ガリレア</t>
+          <t>ガウディ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5269,33 +5268,33 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>45034</v>
+        <v>45007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>モズアスコット</t>
+          <t>レイデオロ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ゴールドテーラー</t>
+          <t>グラディーヴァ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>清水 英克</t>
+          <t>上村 洋行</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>キシダンチョウ</t>
+          <t>ガリレア</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5304,33 +5303,33 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>44956</v>
+        <v>45034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>モズアスコット</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>キャリコ</t>
+          <t>ゴールドテーラー</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>吉岡 辰弥</t>
+          <t>清水 英克</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>キョウエイブリッサ</t>
+          <t>キシダンチョウ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5339,33 +5338,33 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>43929</v>
+        <v>44956</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>グレーターロンドン</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>キョウエイポズナン</t>
+          <t>キャリコ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>武市 康男</t>
+          <t>吉岡 辰弥</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>キンググローリー</t>
+          <t>キョウエイブリッサ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5374,16 +5373,16 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>45008</v>
+        <v>43929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ダノンプレミアム</t>
+          <t>グレーターロンドン</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ハーフムーン2</t>
+          <t>キョウエイポズナン</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5393,67 +5392,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>古賀 慎明</t>
+          <t>武市 康男</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>クイーンズウォーク</t>
+          <t>キンググローリー</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>44269</v>
+        <v>45008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>ダノンプレミアム</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ウェイヴェルアベニュー</t>
+          <t>ハーフムーン2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>中内田 充正</t>
+          <t>古賀 慎明</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>クルゼイロドスル</t>
+          <t>クイーンズウォーク</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>43959</v>
+        <v>44269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ファインニードル</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>スタリア</t>
+          <t>ウェイヴェルアベニュー</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5463,14 +5462,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>高橋 義忠</t>
+          <t>中内田 充正</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>クロワデュノール</t>
+          <t>クルゼイロドスル</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5479,16 +5478,16 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>44641</v>
+        <v>43959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ファインニードル</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ライジングクロス</t>
+          <t>スタリア</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5498,14 +5497,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>斉藤 崇史</t>
+          <t>高橋 義忠</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>グランアルト</t>
+          <t>クロワデュノール</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5514,33 +5513,33 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>44987</v>
+        <v>44641</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ワールドプレミア</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ハクモクレン</t>
+          <t>ライジングクロス</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>斎藤 誠</t>
+          <t>斉藤 崇史</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>グランドプラージュ</t>
+          <t>グランアルト</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5549,33 +5548,33 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>44668</v>
+        <v>44987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>シニスターミニスター</t>
+          <t>ワールドプレミア</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ベルプラージュ</t>
+          <t>ハクモクレン</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>斎藤 誠</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>グリューネグリーン</t>
+          <t>グランドプラージュ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5584,33 +5583,33 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>43892</v>
+        <v>44668</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ラブリーデイ</t>
+          <t>シニスターミニスター</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>レディーダービー</t>
+          <t>ベルプラージュ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>グリーンエナジー</t>
+          <t>グリューネグリーン</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5619,16 +5618,16 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>44955</v>
+        <v>43892</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>スワーヴリチャード</t>
+          <t>ラブリーデイ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>シンバル2</t>
+          <t>レディーダービー</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5638,14 +5637,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>上原 佑紀</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ケイアイシェルビー</t>
+          <t>グリーンエナジー</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5654,33 +5653,33 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>43223</v>
+        <v>44955</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ディープインパクト</t>
+          <t>スワーヴリチャード</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ケイアイガーベラ</t>
+          <t>シンバル2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>平田 修</t>
+          <t>上原 佑紀</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ケイアイドリー</t>
+          <t>ケイアイシェルビー</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5689,16 +5688,16 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>42841</v>
+        <v>43223</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>エスポワールシチー</t>
+          <t>ディープインパクト</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>アルヴェナ</t>
+          <t>ケイアイガーベラ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5708,32 +5707,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>前川 恭子</t>
+          <t>平田 修</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ケリフレッドアスク</t>
+          <t>ケイアイドリー</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>44654</v>
+        <v>42841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ドゥラメンテ</t>
+          <t>エスポワールシチー</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ディープインアスク</t>
+          <t>アルヴェナ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5743,23 +5742,23 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>藤原 英昭</t>
+          <t>前川 恭子</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ゲンパチムサシ</t>
+          <t>ケリフレッドアスク</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>43202</v>
+        <v>44654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5768,24 +5767,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ティアランドール</t>
+          <t>ディープインアスク</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>秋本 大介</t>
+          <t>藤原 英昭</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>コア</t>
+          <t>ゲンパチムサシ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5794,16 +5793,16 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>44593</v>
+        <v>43202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>ドゥラメンテ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>マイダイアリー</t>
+          <t>ティアランドール</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5813,49 +5812,49 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>秋本 大介</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>コウギョク</t>
+          <t>コア</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>45029</v>
+        <v>44593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ハーランズルビー</t>
+          <t>マイダイアリー</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>昆 貢</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>コガネノソラ</t>
+          <t>コウギョク</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5864,51 +5863,51 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>44322</v>
+        <v>45029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ゴールドシップ</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>マイネヒメル</t>
+          <t>ハーランズルビー</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>菊沢 隆徳</t>
+          <t>昆 貢</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>コスモエルヴァル</t>
+          <t>コガネノソラ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>44974</v>
+        <v>44322</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ダノンバラード</t>
+          <t>ゴールドシップ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ヴァニティールールズ</t>
+          <t>マイネヒメル</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5918,14 +5917,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>黒岩 陽一</t>
+          <t>菊沢 隆徳</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>コスモゴレアドール</t>
+          <t>コスモエルヴァル</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5934,16 +5933,16 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>43540</v>
+        <v>44974</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ゴールドシップ</t>
+          <t>ダノンバラード</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>グワダラハラ</t>
+          <t>ヴァニティールールズ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5953,14 +5952,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>秋本 大介</t>
+          <t>黒岩 陽一</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>コスモスプモーニ</t>
+          <t>コスモゴレアドール</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5969,16 +5968,16 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>43960</v>
+        <v>43540</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>リアルインパクト</t>
+          <t>ゴールドシップ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>シャドウライフ</t>
+          <t>グワダラハラ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5988,14 +5987,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>松山 将樹</t>
+          <t>秋本 大介</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>コルテオソレイユ</t>
+          <t>コスモスプモーニ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6004,33 +6003,33 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>44988</v>
+        <v>43960</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ウインブライト</t>
+          <t>リアルインパクト</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ファンシャン</t>
+          <t>シャドウライフ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>佐藤 悠太</t>
+          <t>松山 将樹</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>コレオシークエンス</t>
+          <t>コルテオソレイユ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6039,16 +6038,16 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>45026</v>
+        <v>44988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>サートゥルナーリア</t>
+          <t>ウインブライト</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ノーブルカリナン</t>
+          <t>ファンシャン</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6065,25 +6064,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>コンクイスタ</t>
+          <t>コレオシークエンス</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>43923</v>
+        <v>45026</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>サートゥルナーリア</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ドリームオブジェニー</t>
+          <t>ノーブルカリナン</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6093,32 +6092,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>吉岡 辰弥</t>
+          <t>佐藤 悠太</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>コンドゥイア</t>
+          <t>コンクイスタ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>44667</v>
+        <v>43923</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>フォーウィールドライブ</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ボリード</t>
+          <t>ドリームオブジェニー</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6128,14 +6127,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>井上 智史</t>
+          <t>吉岡 辰弥</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ゴバド</t>
+          <t>コンドゥイア</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,51 +6143,51 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>44995</v>
+        <v>44667</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>トーセンラー</t>
+          <t>フォーウィールドライブ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>シャンデリアスピン</t>
+          <t>ボリード</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>加藤 征弘</t>
+          <t>井上 智史</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ゴーイントゥスカイ</t>
+          <t>ゴバド</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>44997</v>
+        <v>44995</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>コントレイル</t>
+          <t>トーセンラー</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ゴーイントゥザウィンドウ</t>
+          <t>シャンデリアスピン</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6198,14 +6197,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>上原 佑紀</t>
+          <t>加藤 征弘</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>サイモンシャリオ</t>
+          <t>ゴーイントゥスカイ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6214,33 +6213,33 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>44999</v>
+        <v>44997</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>アルアイン</t>
+          <t>コントレイル</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>キュアロージズ</t>
+          <t>ゴーイントゥザウィンドウ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>梅田 智之</t>
+          <t>上原 佑紀</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>サイン</t>
+          <t>サイモンシャリオ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6249,16 +6248,16 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>44997</v>
+        <v>44999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>キセキ</t>
+          <t>アルアイン</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>イヴ</t>
+          <t>キュアロージズ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6268,14 +6267,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>佐藤 悠太</t>
+          <t>梅田 智之</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>サウンドムーブ</t>
+          <t>サイン</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6284,16 +6283,16 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>44980</v>
+        <v>44997</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>リアルスティール</t>
+          <t>キセキ</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>サウンドルチア</t>
+          <t>イヴ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6303,14 +6302,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>斉藤 崇史</t>
+          <t>佐藤 悠太</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>サトノアイボリー</t>
+          <t>サウンドムーブ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6319,16 +6318,16 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>45001</v>
+        <v>44980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>リアルスティール</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ホエールキャプチャ</t>
+          <t>サウンドルチア</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6338,14 +6337,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>斉藤 崇史</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>サトノセプター</t>
+          <t>サトノアイボリー</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6354,16 +6353,16 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>44972</v>
+        <v>45001</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kingman</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>イカット</t>
+          <t>ホエールキャプチャ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6373,14 +6372,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>上村 洋行</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>サトノヴァンクル</t>
+          <t>サトノセプター</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6389,33 +6388,33 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>44966</v>
+        <v>44972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ポエティックフレア</t>
+          <t>Kingman</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>トーセンソレイユ</t>
+          <t>イカット</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>木村 哲也</t>
+          <t>上村 洋行</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>サノノグレーター</t>
+          <t>サトノヴァンクル</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6424,16 +6423,16 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>45014</v>
+        <v>44966</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>グレーターロンドン</t>
+          <t>ポエティックフレア</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>メメクザリアーナ</t>
+          <t>トーセンソレイユ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6443,32 +6442,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>尾形 和幸</t>
+          <t>木村 哲也</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>サムシングスイート</t>
+          <t>サノノグレーター</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>45041</v>
+        <v>45014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>サートゥルナーリア</t>
+          <t>グレーターロンドン</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>サムシングジャスト</t>
+          <t>メメクザリアーナ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6478,14 +6477,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>伊藤 大士</t>
+          <t>尾形 和幸</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>サンセットブライト</t>
+          <t>サムシングスイート</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6494,16 +6493,16 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>44316</v>
+        <v>45041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ホッコータルマエ</t>
+          <t>サートゥルナーリア</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>デルマオサキ</t>
+          <t>サムシングジャスト</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6513,23 +6512,23 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>伊藤 大士</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>サンデーパーティー</t>
+          <t>サンセットブライト</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>44994</v>
+        <v>44316</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6538,7 +6537,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ラフメイカー</t>
+          <t>デルマオサキ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6555,7 +6554,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>サンデーファンデー</t>
+          <t>サンデーパーティー</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6564,33 +6563,33 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>43963</v>
+        <v>44994</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>スズカコーズウェイ</t>
+          <t>ホッコータルマエ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ファーストレディ</t>
+          <t>ラフメイカー</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>東田 明士</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>シックスペンス</t>
+          <t>サンデーファンデー</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6599,33 +6598,33 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>44303</v>
+        <v>43963</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>スズカコーズウェイ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>フィンレイズラッキーチャーム</t>
+          <t>ファーストレディ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>田中 博康</t>
+          <t>東田 明士</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>シャンパンカラー</t>
+          <t>シックスペンス</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6634,16 +6633,16 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>43893</v>
+        <v>44303</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ドゥラメンテ</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>メモリアルライフ</t>
+          <t>フィンレイズラッキーチャーム</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6653,67 +6652,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>田中 剛</t>
+          <t>田中 博康</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>シュガービスケッツ</t>
+          <t>シャンパンカラー</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>45035</v>
+        <v>43893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>マインドユアビスケッツ</t>
+          <t>ドゥラメンテ</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>コマンドゥールキイ</t>
+          <t>メモリアルライフ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>東田 明士</t>
+          <t>田中 剛</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ショウナンアデイブ</t>
+          <t>シュガービスケッツ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>43497</v>
+        <v>45035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ディープインパクト</t>
+          <t>マインドユアビスケッツ</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>シーヴ</t>
+          <t>コマンドゥールキイ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6723,14 +6722,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>高野 友和</t>
+          <t>東田 明士</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ショウナンガルフ</t>
+          <t>ショウナンアデイブ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6739,16 +6738,16 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>44942</v>
+        <v>43497</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ハービンジャー</t>
+          <t>ディープインパクト</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ミカリーニョ</t>
+          <t>シーヴ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6758,32 +6757,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>須貝 尚介</t>
+          <t>高野 友和</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ショウナンバルドル</t>
+          <t>ショウナンガルフ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>44613</v>
+        <v>44942</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ブリックスアンドモルタル</t>
+          <t>ハービンジャー</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>アウェイク</t>
+          <t>ミカリーニョ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6800,25 +6799,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>シーミハットク</t>
+          <t>ショウナンバルドル</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>44992</v>
+        <v>44613</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>オルフェーヴル</t>
+          <t>ブリックスアンドモルタル</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ブルーミンバー</t>
+          <t>アウェイク</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6828,14 +6827,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>寺島 良</t>
+          <t>須貝 尚介</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ジャスティンスカイ</t>
+          <t>シーミハットク</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6844,16 +6843,16 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>43484</v>
+        <v>44992</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>オルフェーヴル</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>リアリサトリス</t>
+          <t>ブルーミンバー</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6863,14 +6862,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>友道 康夫</t>
+          <t>寺島 良</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ジャスティンルマン</t>
+          <t>ジャスティンスカイ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6879,16 +6878,16 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>45032</v>
+        <v>43484</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>スワーヴリチャード</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>イルーシヴハピネス</t>
+          <t>リアリサトリス</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6898,32 +6897,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>友道 康夫</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ジャストビート</t>
+          <t>ジャスティンルマン</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>45020</v>
+        <v>45032</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>デクラレーションオブウォー</t>
+          <t>スワーヴリチャード</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ステルス</t>
+          <t>イルーシヴハピネス</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6933,14 +6932,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>安達 昭夫</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ジョイフルニュース</t>
+          <t>ジャストビート</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6949,51 +6948,51 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>44683</v>
+        <v>45020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>デクラレーションオブウォー</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ジョイニキータ</t>
+          <t>ステルス</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>大竹 正博</t>
+          <t>安達 昭夫</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ジーティーブラック</t>
+          <t>ジョイフルニュース</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>45013</v>
+        <v>44683</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>マイウェイアムール</t>
+          <t>ジョイニキータ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7003,32 +7002,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>菊沢 隆徳</t>
+          <t>大竹 正博</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>スタニングレディ</t>
+          <t>ジーティーブラック</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>44960</v>
+        <v>45013</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ベンバトル</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>フォクシーレディ</t>
+          <t>マイウェイアムール</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7038,32 +7037,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>高木 登</t>
+          <t>菊沢 隆徳</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ストロングエース</t>
+          <t>スタニングレディ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>45012</v>
+        <v>44960</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ヤマカツエース</t>
+          <t>ベンバトル</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>フラヴィニー</t>
+          <t>フォクシーレディ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7073,14 +7072,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>高木 登</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ストームゲイル</t>
+          <t>ストロングエース</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7089,51 +7088,51 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>45030</v>
+        <v>45012</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>タリスマニック</t>
+          <t>ヤマカツエース</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ジャポニウム</t>
+          <t>フラヴィニー</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>四位 洋文</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>スピナーリート</t>
+          <t>ストームゲイル</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>44987</v>
+        <v>45030</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>タリスマニック</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>スピニングメモリーズ</t>
+          <t>ジャポニウム</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7143,49 +7142,49 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>須貝 尚介</t>
+          <t>四位 洋文</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>セイカミナミホリエ</t>
+          <t>スピナーリート</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>45002</v>
+        <v>44987</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>グレーターロンドン</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>セイカフォルトゥナ</t>
+          <t>スピニングメモリーズ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>須貝 尚介</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>セイカンサンラン</t>
+          <t>セイカミナミホリエ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7194,33 +7193,33 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>45005</v>
+        <v>45002</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>カリフォルニアクローム</t>
+          <t>グレーターロンドン</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>シャイニールミナス</t>
+          <t>セイカフォルトゥナ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>大根田 裕之</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ゾロアストロ</t>
+          <t>セイカンサンラン</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7229,33 +7228,33 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>44986</v>
+        <v>45005</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>モーリス</t>
+          <t>カリフォルニアクローム</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>アルミレーナ</t>
+          <t>シャイニールミナス</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>宮田 敬介</t>
+          <t>大根田 裕之</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>タイダルロック</t>
+          <t>ゾロアストロ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7264,7 +7263,7 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>44972</v>
+        <v>44986</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7273,7 +7272,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>アースライズ</t>
+          <t>アルミレーナ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7283,14 +7282,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>武井 亮</t>
+          <t>宮田 敬介</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>タマリスペクト</t>
+          <t>タイダルロック</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,16 +7298,16 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>44997</v>
+        <v>44972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>カリフォルニアクローム</t>
+          <t>モーリス</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ワディアルヒタン</t>
+          <t>アースライズ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7318,14 +7317,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>武井 亮</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ダノンミッション</t>
+          <t>タマリスペクト</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7334,16 +7333,16 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>44643</v>
+        <v>44997</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>カリフォルニアクローム</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>フローレスダンサー</t>
+          <t>ワディアルヒタン</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7353,14 +7352,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>堀 宣行</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>チェイサー</t>
+          <t>ダノンミッション</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7369,16 +7368,16 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>44959</v>
+        <v>44643</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>レイデオロ</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ウェストレー</t>
+          <t>フローレスダンサー</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7388,14 +7387,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>堀 宣行</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>チュウワカーネギー</t>
+          <t>チェイサー</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7404,51 +7403,51 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>44986</v>
+        <v>44959</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>モーリス</t>
+          <t>レイデオロ</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>デックドアウト</t>
+          <t>ウェストレー</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>大久保 龍志</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>テレサ</t>
+          <t>チュウワカーネギー</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44586</v>
+        <v>44986</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>アドマイヤマーズ</t>
+          <t>モーリス</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>タムニア</t>
+          <t>デックドアウト</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7458,32 +7457,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>大久保 龍志</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>テーオーアルアイン</t>
+          <t>テレサ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>44999</v>
+        <v>44586</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>アルアイン</t>
+          <t>アドマイヤマーズ</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>シードラゴン</t>
+          <t>タムニア</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7493,14 +7492,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>奥村 豊</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ディバインウインド</t>
+          <t>テーオーアルアイン</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7509,51 +7508,51 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>44983</v>
+        <v>44999</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>スワーヴリチャード</t>
+          <t>アルアイン</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ストロベリームーン</t>
+          <t>シードラゴン</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>堀 宣行</t>
+          <t>奥村 豊</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>トワニ</t>
+          <t>ディバインウインド</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>44950</v>
+        <v>44983</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>リオンディーズ</t>
+          <t>スワーヴリチャード</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>イニシャルダブル</t>
+          <t>ストロベリームーン</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7563,49 +7562,49 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>蛯名 正義</t>
+          <t>堀 宣行</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ドラゴンブースト</t>
+          <t>トワニ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>44637</v>
+        <v>44950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>スクリーンヒーロー</t>
+          <t>リオンディーズ</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>トーコーディオーネ</t>
+          <t>イニシャルダブル</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>藤野 健太</t>
+          <t>蛯名 正義</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ドンインザムード</t>
+          <t>ドラゴンブースト</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7614,16 +7613,16 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>44688</v>
+        <v>44637</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>アジアエクスプレス</t>
+          <t>スクリーンヒーロー</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ハギノウィッシュ</t>
+          <t>トーコーディオーネ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7633,32 +7632,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>今野 貞一</t>
+          <t>藤野 健太</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ナムラコスモス</t>
+          <t>ドンインザムード</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>45006</v>
+        <v>44688</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ダノンプレミアム</t>
+          <t>アジアエクスプレス</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ナムラリコリス</t>
+          <t>ハギノウィッシュ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7668,32 +7667,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>大橋 勇樹</t>
+          <t>今野 貞一</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ナムラフランク</t>
+          <t>ナムラコスモス</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>43544</v>
+        <v>45006</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ミッキーアイル</t>
+          <t>ダノンプレミアム</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ナムラヒラリー</t>
+          <t>ナムラリコリス</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7703,14 +7702,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>鈴木 孝志</t>
+          <t>大橋 勇樹</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ナリタエスペランサ</t>
+          <t>ナムラフランク</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7719,16 +7718,16 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>45004</v>
+        <v>43544</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ミッキーアイル</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ワンダーフィリー</t>
+          <t>ナムラヒラリー</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7738,14 +7737,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>福永 祐一</t>
+          <t>鈴木 孝志</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ネッタイヤライ</t>
+          <t>ナリタエスペランサ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7754,16 +7753,16 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>44979</v>
+        <v>45004</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>コントレイル</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>サンライズシェル</t>
+          <t>ワンダーフィリー</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7773,14 +7772,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>矢作 芳人</t>
+          <t>福永 祐一</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ノチェセラーダ</t>
+          <t>ネッタイヤライ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7789,16 +7788,16 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>44975</v>
+        <v>44979</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ドレフォン</t>
+          <t>コントレイル</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ノチェブランカ</t>
+          <t>サンライズシェル</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7808,67 +7807,67 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>杉山 佳明</t>
+          <t>矢作 芳人</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ノビリシマビジョン</t>
+          <t>ノチェセラーダ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>44675</v>
+        <v>44975</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>フィエールマン</t>
+          <t>ドレフォン</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>マチカネタマカズラ</t>
+          <t>ノチェブランカ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>青木 孝文</t>
+          <t>杉山 佳明</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ノーウェアマン</t>
+          <t>ノビリシマビジョン</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>45061</v>
+        <v>44675</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>フィエールマン</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>サトノアスカ</t>
+          <t>マチカネタマカズラ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7878,14 +7877,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>浅利 英明</t>
+          <t>青木 孝文</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ノーブルサヴェージ</t>
+          <t>ノーウェアマン</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7894,16 +7893,16 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>45020</v>
+        <v>45061</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>リオンディーズ</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>アグレアーブル</t>
+          <t>サトノアスカ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7913,14 +7912,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>森 一誠</t>
+          <t>浅利 英明</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>バステール</t>
+          <t>ノーブルサヴェージ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7929,33 +7928,33 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>45013</v>
+        <v>45020</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>リオンディーズ</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>マンビア</t>
+          <t>アグレアーブル</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>斉藤 崇史</t>
+          <t>森 一誠</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>パラディオン</t>
+          <t>バステール</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7964,16 +7963,16 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>44946</v>
+        <v>45013</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>レイデオロ</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ステラリード</t>
+          <t>マンビア</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7983,32 +7982,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>高柳 大輔</t>
+          <t>斉藤 崇史</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>パラディレーヌ</t>
+          <t>パラディオン</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>44626</v>
+        <v>44946</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>レイデオロ</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>パラダイスガーデン</t>
+          <t>ステラリード</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8018,23 +8017,23 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>千田 輝彦</t>
+          <t>高柳 大輔</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>パントルナイーフ</t>
+          <t>パラディレーヌ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>45025</v>
+        <v>44626</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8043,24 +8042,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>アールブリュット</t>
+          <t>パラダイスガーデン</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>木村 哲也</t>
+          <t>千田 輝彦</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ビーオンザカバー</t>
+          <t>パントルナイーフ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8069,16 +8068,16 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>44652</v>
+        <v>45025</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ハービンジャー</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>セレブリティモデル</t>
+          <t>アールブリュット</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8088,32 +8087,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>伊藤 圭三</t>
+          <t>木村 哲也</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ピエドゥラパン</t>
+          <t>ビーオンザカバー</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>44951</v>
+        <v>44652</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>ハービンジャー</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>トロワゼトワル</t>
+          <t>セレブリティモデル</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8123,119 +8122,119 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>千葉 直人</t>
+          <t>伊藤 圭三</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ファインライン</t>
+          <t>ピエドゥラパン</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>44312</v>
+        <v>44951</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ファインニードル</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ディープサウス</t>
+          <t>トロワゼトワル</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>松永 幹夫</t>
+          <t>千葉 直人</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ファムクラジューズ</t>
+          <t>ファインライン</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>44976</v>
+        <v>44312</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ベンバトル</t>
+          <t>ファインニードル</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>キューンハイト</t>
+          <t>ディープサウス</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>黒岩 陽一</t>
+          <t>松永 幹夫</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ファーヴェント</t>
+          <t>ファムクラジューズ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C132" s="25" t="n">
-        <v>44248</v>
+        <v>44976</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ハーツクライ</t>
+          <t>ベンバトル</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>トータルヒート</t>
+          <t>キューンハイト</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>藤原 英昭</t>
+          <t>黒岩 陽一</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>フォルテアンジェロ</t>
+          <t>ファーヴェント</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8244,33 +8243,33 @@
         </is>
       </c>
       <c r="C133" s="25" t="n">
-        <v>44960</v>
+        <v>44248</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>フィエールマン</t>
+          <t>ハーツクライ</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>レディアンジェラ</t>
+          <t>トータルヒート</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>上原 佑紀</t>
+          <t>藤原 英昭</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>フォーキャンドルズ</t>
+          <t>フォルテアンジェロ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8279,103 +8278,103 @@
         </is>
       </c>
       <c r="C134" s="25" t="n">
-        <v>44622</v>
+        <v>44960</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>フィエールマン</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>デルマコイウタ</t>
+          <t>レディアンジェラ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>本田 優</t>
+          <t>上原 佑紀</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>フューチャプライム</t>
+          <t>フォーキャンドルズ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C135" s="25" t="n">
-        <v>45000</v>
+        <v>44622</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>サートゥルナーリア</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ハイタッチクイーン</t>
+          <t>デルマコイウタ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>本田 優</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ブエナオンダ</t>
+          <t>フューチャプライム</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C136" s="25" t="n">
-        <v>44216</v>
+        <v>45000</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>リオンディーズ</t>
+          <t>サートゥルナーリア</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>オーサムウインド</t>
+          <t>ハイタッチクイーン</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>須貝 尚介</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ブライトフレア</t>
+          <t>ブエナオンダ</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8384,16 +8383,16 @@
         </is>
       </c>
       <c r="C137" s="25" t="n">
-        <v>45026</v>
+        <v>44216</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ポエティックフレア</t>
+          <t>リオンディーズ</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>クラリスピンク</t>
+          <t>オーサムウインド</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8403,14 +8402,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>佐藤 悠太</t>
+          <t>須貝 尚介</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ブラックオリンピア</t>
+          <t>ブライトフレア</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8419,16 +8418,16 @@
         </is>
       </c>
       <c r="C138" s="25" t="n">
-        <v>44999</v>
+        <v>45026</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ポエティックフレア</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ピノ</t>
+          <t>クラリスピンク</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8438,14 +8437,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>友道 康夫</t>
+          <t>佐藤 悠太</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ブラックシャリマー</t>
+          <t>ブラックオリンピア</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8454,7 +8453,7 @@
         </is>
       </c>
       <c r="C139" s="25" t="n">
-        <v>45045</v>
+        <v>44999</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8463,7 +8462,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>フォークレジェンド</t>
+          <t>ピノ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8473,14 +8472,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>友道 康夫</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ブルースカイブルー</t>
+          <t>ブラックシャリマー</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8489,16 +8488,16 @@
         </is>
       </c>
       <c r="C140" s="25" t="n">
-        <v>44952</v>
+        <v>45045</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ハービンジャー</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>エマノン</t>
+          <t>フォークレジェンド</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8508,14 +8507,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>平田 修</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ブレットパス</t>
+          <t>ブルースカイブルー</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8524,16 +8523,16 @@
         </is>
       </c>
       <c r="C141" s="25" t="n">
-        <v>44981</v>
+        <v>44952</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>アルアイン</t>
+          <t>ハービンジャー</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>パッシングスルー</t>
+          <t>エマノン</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8543,14 +8542,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>中内田 充正</t>
+          <t>平田 修</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>プレシャスデイ</t>
+          <t>ブレットパス</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8559,33 +8558,33 @@
         </is>
       </c>
       <c r="C142" s="25" t="n">
-        <v>44592</v>
+        <v>44981</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ニューイヤーズデイ</t>
+          <t>アルアイン</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>スプレンダークラン</t>
+          <t>パッシングスルー</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>伊坂 重信</t>
+          <t>中内田 充正</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ヘデントール</t>
+          <t>プレシャスデイ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8594,16 +8593,16 @@
         </is>
       </c>
       <c r="C143" s="25" t="n">
-        <v>44292</v>
+        <v>44592</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ルーラーシップ</t>
+          <t>ニューイヤーズデイ</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>コルコバード</t>
+          <t>スプレンダークラン</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8613,14 +8612,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>木村 哲也</t>
+          <t>伊坂 重信</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ベラジオボンド</t>
+          <t>ヘデントール</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8629,33 +8628,33 @@
         </is>
       </c>
       <c r="C144" s="25" t="n">
-        <v>44242</v>
+        <v>44292</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>ルーラーシップ</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ダンサーデスティネイション</t>
+          <t>コルコバード</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>上村 洋行</t>
+          <t>木村 哲也</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ベレシート</t>
+          <t>ベラジオボンド</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8664,16 +8663,16 @@
         </is>
       </c>
       <c r="C145" s="25" t="n">
-        <v>44972</v>
+        <v>44242</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>クロノジェネシス</t>
+          <t>ダンサーデスティネイション</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8683,32 +8682,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>斉藤 崇史</t>
+          <t>上村 洋行</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ペイシャシス</t>
+          <t>ベレシート</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C146" s="25" t="n">
-        <v>45001</v>
+        <v>44972</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>シスキン</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ペイシャフェリス</t>
+          <t>クロノジェネシス</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8718,14 +8717,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>加藤 公太</t>
+          <t>斉藤 崇史</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ペンダント</t>
+          <t>ペイシャシス</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8734,16 +8733,16 @@
         </is>
       </c>
       <c r="C147" s="25" t="n">
-        <v>44993</v>
+        <v>45001</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>オルフェーヴル</t>
+          <t>シスキン</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>スパイラルステップ</t>
+          <t>ペイシャフェリス</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8753,32 +8752,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>池江 泰寿</t>
+          <t>加藤 公太</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ページターナー</t>
+          <t>ペンダント</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C148" s="25" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>オルフェーヴル</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>コールバック</t>
+          <t>スパイラルステップ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8788,67 +8787,67 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>中内田 充正</t>
+          <t>池江 泰寿</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ホーエリート</t>
+          <t>ページターナー</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C149" s="25" t="n">
-        <v>44310</v>
+        <v>44991</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ルーラーシップ</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ゴールデンハープ</t>
+          <t>コールバック</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>田島 俊明</t>
+          <t>中内田 充正</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>マイネルアレス</t>
+          <t>ホーエリート</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C150" s="25" t="n">
-        <v>44631</v>
+        <v>44310</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>スクリーンヒーロー</t>
+          <t>ルーラーシップ</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>リープフラウミルヒ</t>
+          <t>ゴールデンハープ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8858,14 +8857,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>田島 俊明</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>マイネルカンパーナ</t>
+          <t>マイネルアレス</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8874,16 +8873,16 @@
         </is>
       </c>
       <c r="C151" s="25" t="n">
-        <v>43938</v>
+        <v>44631</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ゴールドシップ</t>
+          <t>スクリーンヒーロー</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>マンバラ</t>
+          <t>リープフラウミルヒ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8893,14 +8892,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>青木 孝文</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>マイネルグロン</t>
+          <t>マイネルカンパーナ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8909,7 +8908,7 @@
         </is>
       </c>
       <c r="C152" s="25" t="n">
-        <v>43258</v>
+        <v>43938</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -8918,7 +8917,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>マイネヌーヴェル</t>
+          <t>マンバラ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8935,7 +8934,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>マイネルシンベリン</t>
+          <t>マイネルグロン</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8944,16 +8943,16 @@
         </is>
       </c>
       <c r="C153" s="25" t="n">
-        <v>45035</v>
+        <v>43258</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>リオンディーズ</t>
+          <t>ゴールドシップ</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>フォトジェニック</t>
+          <t>マイネヌーヴェル</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8963,14 +8962,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>武市 康男</t>
+          <t>青木 孝文</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>マイネルゼーロス</t>
+          <t>マイネルシンベリン</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8979,16 +8978,16 @@
         </is>
       </c>
       <c r="C154" s="25" t="n">
-        <v>45014</v>
+        <v>45035</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ダノンバラード</t>
+          <t>リオンディーズ</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>マイネアルデュール</t>
+          <t>フォトジェニック</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8998,14 +8997,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>武市 康男</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>マイネルフォルツァ</t>
+          <t>マイネルゼーロス</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9014,16 +9013,16 @@
         </is>
       </c>
       <c r="C155" s="25" t="n">
-        <v>43958</v>
+        <v>45014</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ゴールドシップ</t>
+          <t>ダノンバラード</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ラッフォルツァート</t>
+          <t>マイネアルデュール</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9033,14 +9032,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>金成 貴史</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>マイネルマスター</t>
+          <t>マイネルフォルツァ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9049,16 +9048,16 @@
         </is>
       </c>
       <c r="C156" s="25" t="n">
-        <v>45026</v>
+        <v>43958</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>ゴールドシップ</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>コスモバルバラ</t>
+          <t>ラッフォルツァート</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9068,14 +9067,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>青木 孝文</t>
+          <t>金成 貴史</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>マイネルモメンタム</t>
+          <t>マイネルマスター</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9084,16 +9083,16 @@
         </is>
       </c>
       <c r="C157" s="25" t="n">
-        <v>44251</v>
+        <v>45026</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ゴールドシップ</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>マイネアルデュール</t>
+          <t>コスモバルバラ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9103,14 +9102,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>青木 孝文</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>マイネルヴェーゼン</t>
+          <t>マイネルモメンタム</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9119,16 +9118,16 @@
         </is>
       </c>
       <c r="C158" s="25" t="n">
-        <v>44992</v>
+        <v>44251</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ベンバトル</t>
+          <t>ゴールドシップ</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ペルソナリテ</t>
+          <t>マイネアルデュール</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9145,7 +9144,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>マグナレガリア</t>
+          <t>マイネルヴェーゼン</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9154,16 +9153,16 @@
         </is>
       </c>
       <c r="C159" s="25" t="n">
-        <v>44268</v>
+        <v>44992</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>レイデオロ</t>
+          <t>ベンバトル</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>デライトポイント</t>
+          <t>ペルソナリテ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9180,25 +9179,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>マツリダイコ</t>
+          <t>マグナレガリア</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C160" s="25" t="n">
-        <v>44982</v>
+        <v>44268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>レイデオロ</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>サラフィナ</t>
+          <t>デライトポイント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9208,67 +9207,67 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>黒岩 陽一</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>マテンロウゲイル</t>
+          <t>マツリダイコ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C161" s="25" t="n">
-        <v>44977</v>
+        <v>44982</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>デザートライド</t>
+          <t>サラフィナ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>野中 賢二</t>
+          <t>黒岩 陽一</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>マテンロウスカイ</t>
+          <t>マテンロウゲイル</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C162" s="25" t="n">
-        <v>43501</v>
+        <v>44977</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>モーリス</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>レッドラヴィータ</t>
+          <t>デザートライド</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9278,32 +9277,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>松永 幹夫</t>
+          <t>野中 賢二</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ミスティックレナン</t>
+          <t>マテンロウスカイ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C163" s="25" t="n">
-        <v>45003</v>
+        <v>43501</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Cracksman</t>
+          <t>モーリス</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rue Renan</t>
+          <t>レッドラヴィータ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9313,32 +9312,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>上村 洋行</t>
+          <t>松永 幹夫</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ミステリーウェイ</t>
+          <t>ミスティックレナン</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C164" s="25" t="n">
-        <v>43171</v>
+        <v>45003</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ジャスタウェイ</t>
+          <t>Cracksman</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ジプシーハイウェイ</t>
+          <t>Rue Renan</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9348,32 +9347,32 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>小林 真也</t>
+          <t>上村 洋行</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ミッキーヌチバナ</t>
+          <t>ミステリーウェイ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C165" s="25" t="n">
-        <v>43172</v>
+        <v>43171</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ダノンレジェンド</t>
+          <t>ジャスタウェイ</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ヌチバナ</t>
+          <t>ジプシーハイウェイ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9383,49 +9382,49 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>高橋 亮</t>
+          <t>小林 真也</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ミラーダカリエンテ</t>
+          <t>ミッキーヌチバナ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C166" s="25" t="n">
-        <v>44633</v>
+        <v>43172</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>スクリーンヒーロー</t>
+          <t>ダノンレジェンド</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>マイネアルデュール</t>
+          <t>ヌチバナ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>相沢 郁</t>
+          <t>高橋 亮</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>メイショウハッケイ</t>
+          <t>ミラーダカリエンテ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9434,51 +9433,51 @@
         </is>
       </c>
       <c r="C167" s="25" t="n">
-        <v>45013</v>
+        <v>44633</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ダイワメジャー</t>
+          <t>スクリーンヒーロー</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>メイショウヒサカタ</t>
+          <t>マイネアルデュール</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>本田 優</t>
+          <t>相沢 郁</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>メイショウフンジン</t>
+          <t>メイショウハッケイ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C168" s="25" t="n">
-        <v>43217</v>
+        <v>45013</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ホッコータルマエ</t>
+          <t>ダイワメジャー</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>シニスタークイーン</t>
+          <t>メイショウヒサカタ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9488,14 +9487,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>秋山 真一郎</t>
+          <t>本田 優</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ヤコブセン</t>
+          <t>メイショウフンジン</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9504,33 +9503,33 @@
         </is>
       </c>
       <c r="C169" s="25" t="n">
-        <v>44654</v>
+        <v>43217</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>ホッコータルマエ</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>スマッシュ</t>
+          <t>シニスタークイーン</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>斎藤 誠</t>
+          <t>秋山 真一郎</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ライヒスアドラー</t>
+          <t>ヤコブセン</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9539,16 +9538,16 @@
         </is>
       </c>
       <c r="C170" s="25" t="n">
-        <v>45010</v>
+        <v>44654</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>シスキン</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>クライリング</t>
+          <t>スマッシュ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9558,32 +9557,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>上原 佑紀</t>
+          <t>斎藤 誠</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ラフターラインズ</t>
+          <t>ライヒスアドラー</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C171" s="25" t="n">
-        <v>44963</v>
+        <v>45010</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>アルアイン</t>
+          <t>シスキン</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>バンゴール</t>
+          <t>クライリング</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9593,14 +9592,14 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>小笠 倫弘</t>
+          <t>上原 佑紀</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ラベルセーヌ</t>
+          <t>ラフターラインズ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9609,16 +9608,16 @@
         </is>
       </c>
       <c r="C172" s="25" t="n">
-        <v>44966</v>
+        <v>44963</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>アルアイン</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ラフォルス</t>
+          <t>バンゴール</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9628,49 +9627,49 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>鹿戸 雄一</t>
+          <t>小笠 倫弘</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ララファキュルテ</t>
+          <t>ラベルセーヌ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C173" s="25" t="n">
-        <v>45000</v>
+        <v>44966</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>シスキン</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ビットレート</t>
+          <t>ラフォルス</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>斉藤 崇史</t>
+          <t>鹿戸 雄一</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ランスオブカオス</t>
+          <t>ララファキュルテ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9679,16 +9678,16 @@
         </is>
       </c>
       <c r="C174" s="25" t="n">
-        <v>44647</v>
+        <v>45000</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>シスキン</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ハイドラン</t>
+          <t>ビットレート</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9698,14 +9697,14 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>奥村 豊</t>
+          <t>斉藤 崇史</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ラヴェニュー</t>
+          <t>ランスオブカオス</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9714,16 +9713,16 @@
         </is>
       </c>
       <c r="C175" s="25" t="n">
-        <v>45003</v>
+        <v>44647</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>コンテスティッド</t>
+          <t>ハイドラン</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9733,14 +9732,14 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>友道 康夫</t>
+          <t>奥村 豊</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ラージアンサンブル</t>
+          <t>ラヴェニュー</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9749,33 +9748,33 @@
         </is>
       </c>
       <c r="C176" s="25" t="n">
-        <v>44978</v>
+        <v>45003</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ベンバトル</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ナスノフォルテ</t>
+          <t>コンテスティッド</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>武井 亮</t>
+          <t>友道 康夫</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>リアライズシリウス</t>
+          <t>ラージアンサンブル</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9784,16 +9783,16 @@
         </is>
       </c>
       <c r="C177" s="25" t="n">
-        <v>44999</v>
+        <v>44978</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ポエティックフレア</t>
+          <t>ベンバトル</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>レッドミラベル</t>
+          <t>ナスノフォルテ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9803,14 +9802,14 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>手塚 貴久</t>
+          <t>武井 亮</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>リアライズブラーヴ</t>
+          <t>リアライズシリウス</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9819,51 +9818,51 @@
         </is>
       </c>
       <c r="C178" s="25" t="n">
-        <v>45017</v>
+        <v>44999</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>ポエティックフレア</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>イルーシヴキャット</t>
+          <t>レッドミラベル</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>手塚 貴久</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>リアライズルミナス</t>
+          <t>リアライズブラーヴ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C179" s="25" t="n">
-        <v>45019</v>
+        <v>45017</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ジュルビアン</t>
+          <t>イルーシヴキャット</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9873,14 +9872,14 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>橋口 慎介</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>リスレジャンデール</t>
+          <t>リアライズルミナス</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9889,33 +9888,33 @@
         </is>
       </c>
       <c r="C180" s="25" t="n">
-        <v>45003</v>
+        <v>45019</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>シルバーステート</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>リリーズキャンドル</t>
+          <t>ジュルビアン</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>栗田 徹</t>
+          <t>橋口 慎介</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>リピ</t>
+          <t>リスレジャンデール</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9924,51 +9923,51 @@
         </is>
       </c>
       <c r="C181" s="25" t="n">
-        <v>44971</v>
+        <v>45003</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>イースターアイランド</t>
+          <t>リリーズキャンドル</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>西園 翔太</t>
+          <t>栗田 徹</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>レディントン</t>
+          <t>リピ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C182" s="25" t="n">
-        <v>44275</v>
+        <v>44971</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>サトノアラジン</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>クラウンアスリート</t>
+          <t>イースターアイランド</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9978,32 +9977,32 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>西園 翔太</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>レベルスルール</t>
+          <t>レディントン</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C183" s="25" t="n">
-        <v>44594</v>
+        <v>44275</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>イスラボニータ</t>
+          <t>サトノアラジン</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ロックディスタウン</t>
+          <t>クラウンアスリート</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10013,14 +10012,14 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>池江 泰寿</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ロブチェン</t>
+          <t>レベルスルール</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10029,16 +10028,16 @@
         </is>
       </c>
       <c r="C184" s="25" t="n">
-        <v>45025</v>
+        <v>44594</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ワールドプレミア</t>
+          <t>イスラボニータ</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ソングライティング</t>
+          <t>ロックディスタウン</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10048,32 +10047,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>杉山 晴紀</t>
+          <t>池江 泰寿</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ロングトールサリー</t>
+          <t>ロブチェン</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>牝</t>
+          <t>牡</t>
         </is>
       </c>
       <c r="C185" s="25" t="n">
-        <v>44976</v>
+        <v>45025</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ワールドプレミア</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>グローバルビューティ</t>
+          <t>ソングライティング</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10083,84 +10082,84 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>福永 祐一</t>
+          <t>杉山 晴紀</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ロングラン</t>
+          <t>ロングトールサリー</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>せん</t>
+          <t>牝</t>
         </is>
       </c>
       <c r="C186" s="25" t="n">
-        <v>43140</v>
+        <v>44976</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ヴィクトワールピサ</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ノッテビアンカ</t>
+          <t>グローバルビューティ</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>美浦</t>
+          <t>栗東</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>和田 勇介</t>
+          <t>福永 祐一</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ロードフィレール</t>
+          <t>ロングラン</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>せん</t>
         </is>
       </c>
       <c r="C187" s="25" t="n">
-        <v>45003</v>
+        <v>43140</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>キズナ</t>
+          <t>ヴィクトワールピサ</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>プレミアムギフト</t>
+          <t>ノッテビアンカ</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>栗東</t>
+          <t>美浦</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>吉岡 辰弥</t>
+          <t>和田 勇介</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ローベルクランツ</t>
+          <t>ロードフィレール</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10169,16 +10168,16 @@
         </is>
       </c>
       <c r="C188" s="25" t="n">
-        <v>44968</v>
+        <v>45003</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>サトノダイヤモンド</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ブルーメンクローネ</t>
+          <t>プレミアムギフト</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10188,14 +10187,14 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>小林 真也</t>
+          <t>吉岡 辰弥</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ヴィサージュ</t>
+          <t>ローベルクランツ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -10204,16 +10203,16 @@
         </is>
       </c>
       <c r="C189" s="25" t="n">
-        <v>44994</v>
+        <v>44968</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>サトノダイヤモンド</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>メダリオンモチーフ</t>
+          <t>ブルーメンクローネ</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10223,14 +10222,14 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>大久保 龍志</t>
+          <t>小林 真也</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ヴィヴァン</t>
+          <t>ヴィサージュ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10239,16 +10238,16 @@
         </is>
       </c>
       <c r="C190" s="25" t="n">
-        <v>43156</v>
+        <v>44994</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ハーツクライ</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>キトゥンズクイーン</t>
+          <t>メダリオンモチーフ</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10258,14 +10257,14 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>池江 泰寿</t>
+          <t>大久保 龍志</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ヴェルテンベルク</t>
+          <t>ヴィヴァン</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -10274,16 +10273,16 @@
         </is>
       </c>
       <c r="C191" s="25" t="n">
-        <v>43953</v>
+        <v>43156</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ハーツクライ</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>マルカアイチャン</t>
+          <t>キトゥンズクイーン</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10293,40 +10292,75 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>宮本 博</t>
+          <t>池江 泰寿</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>ヴェルテンベルク</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>牡</t>
+        </is>
+      </c>
+      <c r="C192" s="25" t="n">
+        <v>43953</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>キタサンブラック</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>マルカアイチャン</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>栗東</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>宮本 博</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>ヴォラヴィア</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>牡</t>
         </is>
       </c>
-      <c r="C192" s="25" t="n">
+      <c r="C193" s="25" t="n">
         <v>44658</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>エイシンフラッシュ</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>パリュール</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>栗東</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>杉山 佳明</t>
         </is>
@@ -11467,7 +11501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="20.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14281,799 +14315,816 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>プレミアムギフト</t>
-        </is>
-      </c>
-      <c r="B148" s="25" t="n">
-        <v>42447</v>
+          <t>プティフォリー</t>
+        </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>オルフェーヴル</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>インディアナギャル</t>
+          <t>Pretty Please</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ベルプラージュ</t>
+          <t>プレミアムギフト</t>
         </is>
       </c>
       <c r="B149" s="25" t="n">
-        <v>40576</v>
+        <v>42447</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>キングカメハメハ</t>
+          <t>オルフェーヴル</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ベルフィーチャー</t>
+          <t>インディアナギャル</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ペイシャフェリス</t>
+          <t>ベルプラージュ</t>
         </is>
       </c>
       <c r="B150" s="25" t="n">
-        <v>40620</v>
+        <v>40576</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>スペシャルウィーク</t>
+          <t>キングカメハメハ</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>プレザントケイプ</t>
+          <t>ベルフィーチャー</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ペルソナリテ</t>
+          <t>ペイシャフェリス</t>
         </is>
       </c>
       <c r="B151" s="25" t="n">
-        <v>41347</v>
+        <v>40620</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ステイゴールド</t>
+          <t>スペシャルウィーク</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>マイネアルデュール</t>
+          <t>プレザントケイプ</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ホエールキャプチャ</t>
+          <t>ペルソナリテ</t>
         </is>
       </c>
       <c r="B152" s="25" t="n">
-        <v>39502</v>
+        <v>41347</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>クロフネ</t>
+          <t>ステイゴールド</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>グローバルピース</t>
+          <t>マイネアルデュール</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ボリード</t>
+          <t>ホエールキャプチャ</t>
         </is>
       </c>
       <c r="B153" s="25" t="n">
-        <v>41744</v>
+        <v>39502</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ディープインパクト</t>
+          <t>クロフネ</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ヴィクトリアズワイルドキャット</t>
+          <t>グローバルピース</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>マイウェイアムール</t>
+          <t>ボリード</t>
         </is>
       </c>
       <c r="B154" s="25" t="n">
-        <v>42095</v>
+        <v>41744</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>ディープインパクト</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>レイズユアグラス</t>
+          <t>ヴィクトリアズワイルドキャット</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>マイダイアリー</t>
+          <t>マイウェイアムール</t>
         </is>
       </c>
       <c r="B155" s="25" t="n">
-        <v>42495</v>
+        <v>42095</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Frankel</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Diary</t>
+          <t>レイズユアグラス</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>マイネアルデュール</t>
+          <t>マイダイアリー</t>
         </is>
       </c>
       <c r="B156" s="25" t="n">
-        <v>38444</v>
+        <v>42495</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>アドマイヤコジーン</t>
+          <t>Frankel</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>コスモハーティネス</t>
+          <t>Diary</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>マイネヌーヴェル</t>
+          <t>マイネアルデュール</t>
         </is>
       </c>
       <c r="B157" s="25" t="n">
-        <v>36602</v>
+        <v>38444</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ブライアンズタイム</t>
+          <t>アドマイヤコジーン</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>マイネプリテンダー</t>
+          <t>コスモハーティネス</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>マイネヒメル</t>
+          <t>マイネヌーヴェル</t>
         </is>
       </c>
       <c r="B158" s="25" t="n">
-        <v>39866</v>
+        <v>36602</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ロージズインメイ</t>
+          <t>ブライアンズタイム</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>コスモチェーロ</t>
+          <t>マイネプリテンダー</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>マチカネタマカズラ</t>
+          <t>マイネヒメル</t>
         </is>
       </c>
       <c r="B159" s="25" t="n">
-        <v>37684</v>
+        <v>39866</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kingmambo</t>
+          <t>ロージズインメイ</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sweet and Ready</t>
+          <t>コスモチェーロ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>マナローラ</t>
+          <t>マチカネタマカズラ</t>
         </is>
       </c>
       <c r="B160" s="25" t="n">
-        <v>41768</v>
+        <v>37684</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ハーツクライ</t>
+          <t>Kingmambo</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>シェープアップ</t>
+          <t>Sweet and Ready</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>マルカアイチャン</t>
+          <t>マナローラ</t>
         </is>
       </c>
       <c r="B161" s="25" t="n">
-        <v>37714</v>
+        <v>41768</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>フレンチデピュティ</t>
+          <t>ハーツクライ</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>マルカコマチ</t>
+          <t>シェープアップ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>マンバラ</t>
-        </is>
+          <t>マルカアイチャン</t>
+        </is>
+      </c>
+      <c r="B162" s="25" t="n">
+        <v>37714</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Linamix</t>
+          <t>フレンチデピュティ</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Do the Mambo</t>
+          <t>マルカコマチ</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>マンビア</t>
+          <t>マンバラ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Aldebaran</t>
+          <t>Linamix</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Algoa</t>
+          <t>Do the Mambo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ミカリーニョ</t>
-        </is>
-      </c>
-      <c r="B164" s="25" t="n">
-        <v>42109</v>
+          <t>マンビア</t>
+        </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ハーツクライ</t>
+          <t>Aldebaran</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ミスエーニョ</t>
+          <t>Algoa</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ミスベジル</t>
-        </is>
+          <t>ミカリーニョ</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="n">
+        <v>42109</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Medaglia d'Oro</t>
+          <t>ハーツクライ</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Quiet Dance</t>
+          <t>ミスエーニョ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ミュゼミランダ</t>
-        </is>
-      </c>
-      <c r="B166" s="25" t="n">
-        <v>40589</v>
+          <t>ミスベジル</t>
+        </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ダイワメジャー</t>
+          <t>Medaglia d'Oro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>オウリエット</t>
+          <t>Quiet Dance</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>メイショウヒサカタ</t>
+          <t>ミュゼミランダ</t>
         </is>
       </c>
       <c r="B167" s="25" t="n">
-        <v>42109</v>
+        <v>40589</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>シニスターミニスター</t>
+          <t>ダイワメジャー</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>メイショウマンテン</t>
+          <t>オウリエット</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>メダリオンモチーフ</t>
+          <t>メイショウヒサカタ</t>
         </is>
       </c>
       <c r="B168" s="25" t="n">
-        <v>42142</v>
+        <v>42109</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>キングカメハメハ</t>
+          <t>シニスターミニスター</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>パーフェクトジョイ</t>
+          <t>メイショウマンテン</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>メメクザリアーナ</t>
-        </is>
+          <t>メダリオンモチーフ</t>
+        </is>
+      </c>
+      <c r="B169" s="25" t="n">
+        <v>42142</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ジャングルポケット</t>
+          <t>キングカメハメハ</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ピエナビーナス</t>
+          <t>パーフェクトジョイ</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>メモリアルライフ</t>
+          <t>メメクザリアーナ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Reckless Abandon</t>
+          <t>ジャングルポケット</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Baldovina</t>
+          <t>ピエナビーナス</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ライクザウインド</t>
-        </is>
-      </c>
-      <c r="B171" s="25" t="n">
-        <v>36606</v>
+          <t>メモリアルライフ</t>
+        </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Danehill</t>
+          <t>Reckless Abandon</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ウインドインハーヘア</t>
+          <t>Baldovina</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ライジングクロス</t>
-        </is>
+          <t>ライクザウインド</t>
+        </is>
+      </c>
+      <c r="B172" s="25" t="n">
+        <v>36606</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cape Cross</t>
+          <t>Danehill</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Woodrising</t>
+          <t>ウインドインハーヘア</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ライツェント</t>
-        </is>
-      </c>
-      <c r="B173" s="25" t="n">
-        <v>39191</v>
+          <t>ライジングクロス</t>
+        </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>スペシャルウィーク</t>
+          <t>Cape Cross</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ソニンク</t>
+          <t>Woodrising</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ラダームブランシェ</t>
+          <t>ライツェント</t>
         </is>
       </c>
       <c r="B174" s="25" t="n">
-        <v>40982</v>
+        <v>39191</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>チチカステナンゴ</t>
+          <t>スペシャルウィーク</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>アーデルハイト</t>
+          <t>ソニンク</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ラッフォルツァート</t>
+          <t>ラダームブランシェ</t>
         </is>
       </c>
       <c r="B175" s="25" t="n">
-        <v>40953</v>
+        <v>40982</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>グラスワンダー</t>
+          <t>チチカステナンゴ</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>コスモベル</t>
+          <t>アーデルハイト</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ラフォルス</t>
-        </is>
+          <t>ラッフォルツァート</t>
+        </is>
+      </c>
+      <c r="B176" s="25" t="n">
+        <v>40953</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>グラスワンダー</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>La Miraculeuse</t>
+          <t>コスモベル</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ラフメイカー</t>
-        </is>
-      </c>
-      <c r="B177" s="25" t="n">
-        <v>41766</v>
+          <t>ラフォルス</t>
+        </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>スズカマンボ</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ミスワキジャパン</t>
+          <t>La Miraculeuse</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>リアリサトリス</t>
-        </is>
+          <t>ラフメイカー</t>
+        </is>
+      </c>
+      <c r="B178" s="25" t="n">
+        <v>41766</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Numerous</t>
+          <t>スズカマンボ</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Riziere</t>
+          <t>ミスワキジャパン</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>リリーズキャンドル</t>
+          <t>リアリサトリス</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Style Vendome</t>
+          <t>Numerous</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Golden Lily</t>
+          <t>Riziere</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>リープフラウミルヒ</t>
-        </is>
-      </c>
-      <c r="B180" s="25" t="n">
-        <v>42091</v>
+          <t>リリーズキャンドル</t>
+        </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ステイゴールド</t>
+          <t>Style Vendome</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ピノブラン</t>
+          <t>Golden Lily</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ルパン2</t>
-        </is>
+          <t>リープフラウミルヒ</t>
+        </is>
+      </c>
+      <c r="B181" s="25" t="n">
+        <v>42091</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Medaglia d'Oro</t>
+          <t>ステイゴールド</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Promising Lead</t>
+          <t>ピノブラン</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>レッドミラベル</t>
-        </is>
-      </c>
-      <c r="B182" s="25" t="n">
-        <v>41685</v>
+          <t>ルパン2</t>
+        </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ステイゴールド</t>
+          <t>Medaglia d'Oro</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ダンスーズデトワール</t>
+          <t>Promising Lead</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>レッドラヴィータ</t>
+          <t>レッドミラベル</t>
         </is>
       </c>
       <c r="B183" s="25" t="n">
-        <v>40596</v>
+        <v>41685</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>スペシャルウィーク</t>
+          <t>ステイゴールド</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ディクシージャズ</t>
+          <t>ダンスーズデトワール</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>レディアンジェラ</t>
-        </is>
+          <t>レッドラヴィータ</t>
+        </is>
+      </c>
+      <c r="B184" s="25" t="n">
+        <v>40596</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Dark Angel</t>
+          <t>スペシャルウィーク</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Marlinka</t>
+          <t>ディクシージャズ</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>レディーダービー</t>
-        </is>
-      </c>
-      <c r="B185" s="25" t="n">
-        <v>37330</v>
+          <t>レディアンジェラ</t>
+        </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>スペシャルウィーク</t>
+          <t>Dark Angel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ウメノファイバー</t>
+          <t>Marlinka</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ロックディスタウン</t>
+          <t>レディーダービー</t>
         </is>
       </c>
       <c r="B186" s="25" t="n">
-        <v>42050</v>
+        <v>37330</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>オルフェーヴル</t>
+          <t>スペシャルウィーク</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ストレイキャット</t>
+          <t>ウメノファイバー</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ワディアルヒタン</t>
+          <t>ロックディスタウン</t>
         </is>
       </c>
       <c r="B187" s="25" t="n">
-        <v>44997</v>
+        <v>42050</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>タイキシャトル</t>
+          <t>オルフェーヴル</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ワディラム</t>
+          <t>ストレイキャット</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ワンダーフィリー</t>
-        </is>
+          <t>ワディアルヒタン</t>
+        </is>
+      </c>
+      <c r="B188" s="25" t="n">
+        <v>44997</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Invincible Spirit</t>
+          <t>タイキシャトル</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Wicken Wonder</t>
+          <t>ワディラム</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
+          <t>ワンダーフィリー</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Invincible Spirit</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Wicken Wonder</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>ヴァニティールールズ</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>New Approach</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>Miss Pinkerton</t>
         </is>
